--- a/Exam/gymtrackerpro/lib/repository/__tests__/bbt/user-repository/updateMember-bbt-form.xlsx
+++ b/Exam/gymtrackerpro/lib/repository/__tests__/bbt/user-repository/updateMember-bbt-form.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="293" uniqueCount="128">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="280" uniqueCount="108">
   <si>
     <t>Statement: UserRepository.updateMember(memberId, data) – atomically updates Member and User.</t>
   </si>
@@ -154,111 +154,102 @@
     <t>memberId = ""</t>
   </si>
   <si>
+    <t>memberId = "a" (inex)</t>
+  </si>
+  <si>
+    <t>memberId = "a" (exist)</t>
+  </si>
+  <si>
+    <t>Email field</t>
+  </si>
+  <si>
+    <t>email = undefined</t>
+  </si>
+  <si>
+    <t>email = ""</t>
+  </si>
+  <si>
+    <t>email = "a"</t>
+  </si>
+  <si>
+    <t>FullName field</t>
+  </si>
+  <si>
+    <t>fullName = undefined</t>
+  </si>
+  <si>
+    <t>fullName = ""</t>
+  </si>
+  <si>
+    <t>fullName = "A"</t>
+  </si>
+  <si>
+    <t>Phone field</t>
+  </si>
+  <si>
+    <t>phone = undefined</t>
+  </si>
+  <si>
+    <t>phone = ""</t>
+  </si>
+  <si>
+    <t>phone = "a"</t>
+  </si>
+  <si>
+    <t>DOB field</t>
+  </si>
+  <si>
+    <t>dateOfBirth = undefined</t>
+  </si>
+  <si>
+    <t>dateOfBirth = ""</t>
+  </si>
+  <si>
+    <t>dateOfBirth = "a"</t>
+  </si>
+  <si>
+    <t>Password field</t>
+  </si>
+  <si>
+    <t>password = undefined</t>
+  </si>
+  <si>
+    <t>password = ""</t>
+  </si>
+  <si>
+    <t>password = "a"</t>
+  </si>
+  <si>
+    <t>Membership field</t>
+  </si>
+  <si>
+    <t>membershipStart = undefined</t>
+  </si>
+  <si>
+    <t>membershipStart = ""</t>
+  </si>
+  <si>
+    <t>membershipStart = "a"</t>
+  </si>
+  <si>
+    <t>BVA</t>
+  </si>
+  <si>
+    <t>BVA-1 EmptyID</t>
+  </si>
+  <si>
+    <t>BVA-2 InexCharID</t>
+  </si>
+  <si>
     <t>memberId = "a"</t>
   </si>
   <si>
-    <t>Email field</t>
-  </si>
-  <si>
-    <t>email = undefined</t>
-  </si>
-  <si>
-    <t>email = ""</t>
-  </si>
-  <si>
-    <t>email = "a"</t>
-  </si>
-  <si>
-    <t>FullName field</t>
-  </si>
-  <si>
-    <t>fullName = undefined</t>
-  </si>
-  <si>
-    <t>fullName = ""</t>
-  </si>
-  <si>
-    <t>fullName = "A"</t>
-  </si>
-  <si>
-    <t>Phone field</t>
-  </si>
-  <si>
-    <t>phone = undefined</t>
-  </si>
-  <si>
-    <t>phone = ""</t>
-  </si>
-  <si>
-    <t>phone = "a"</t>
-  </si>
-  <si>
-    <t>DOB field</t>
-  </si>
-  <si>
-    <t>dateOfBirth = undefined</t>
-  </si>
-  <si>
-    <t>dateOfBirth = ""</t>
-  </si>
-  <si>
-    <t>dateOfBirth = "a"</t>
-  </si>
-  <si>
-    <t>Password field</t>
-  </si>
-  <si>
-    <t>password = undefined</t>
-  </si>
-  <si>
-    <t>password = ""</t>
-  </si>
-  <si>
-    <t>password = "a"</t>
-  </si>
-  <si>
-    <t>Membership field</t>
-  </si>
-  <si>
-    <t>membershipStart = undefined</t>
-  </si>
-  <si>
-    <t>membershipStart = ""</t>
-  </si>
-  <si>
-    <t>membershipStart = "a"</t>
-  </si>
-  <si>
-    <t>BVA</t>
-  </si>
-  <si>
-    <t>BVA-1 EmptyID</t>
-  </si>
-  <si>
-    <t>BVA-2 OneCharID</t>
-  </si>
-  <si>
-    <t>BVA-3 UndefEmail</t>
+    <t>BVA-3 ExistCharID</t>
   </si>
   <si>
     <t>Updates successfully</t>
   </si>
   <si>
-    <t>BVA-4 EmptyEmail</t>
-  </si>
-  <si>
-    <t>BVA-5 CharEmail</t>
-  </si>
-  <si>
-    <t>BVA-6 UndefName</t>
-  </si>
-  <si>
-    <t>BVA-7 EmptyName</t>
-  </si>
-  <si>
-    <t>BVA-8 CharName</t>
-  </si>
-  <si>
     <t>TC from EC</t>
   </si>
   <si>
@@ -307,58 +298,7 @@
     <t>BVA-3</t>
   </si>
   <si>
-    <t>Returns items</t>
-  </si>
-  <si>
-    <t>BVA-4</t>
-  </si>
-  <si>
-    <t>BVA-5</t>
-  </si>
-  <si>
-    <t>BVA-6</t>
-  </si>
-  <si>
-    <t>BVA-7</t>
-  </si>
-  <si>
-    <t>BVA-8</t>
-  </si>
-  <si>
-    <t>BVA-9</t>
-  </si>
-  <si>
-    <t>BVA-10</t>
-  </si>
-  <si>
-    <t>BVA-11</t>
-  </si>
-  <si>
-    <t>BVA-12</t>
-  </si>
-  <si>
-    <t>BVA-13</t>
-  </si>
-  <si>
-    <t>BVA-14</t>
-  </si>
-  <si>
-    <t>BVA-15</t>
-  </si>
-  <si>
-    <t>BVA-16</t>
-  </si>
-  <si>
-    <t>BVA-17</t>
-  </si>
-  <si>
-    <t>BVA-18</t>
-  </si>
-  <si>
-    <t>BVA-19</t>
-  </si>
-  <si>
-    <t>BVA-20</t>
+    <t>Various field updates</t>
   </si>
   <si>
     <t>Testing</t>
@@ -1133,7 +1073,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C21"/>
+  <dimension ref="A1:C22"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -1179,10 +1119,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C4" s="1" t="s">
         <v>46</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="5" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -1190,7 +1130,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>1</v>
+        <v>47</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>48</v>
@@ -1212,10 +1152,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C7" s="1" t="s">
         <v>50</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>51</v>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -1223,7 +1163,7 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>1</v>
+        <v>51</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>52</v>
@@ -1245,10 +1185,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C10" s="1" t="s">
         <v>54</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>55</v>
       </c>
     </row>
     <row r="11" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -1256,7 +1196,7 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>1</v>
+        <v>55</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>56</v>
@@ -1278,10 +1218,10 @@
         <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C13" s="1" t="s">
         <v>58</v>
-      </c>
-      <c r="C13" s="1" t="s">
-        <v>59</v>
       </c>
     </row>
     <row r="14" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -1289,7 +1229,7 @@
         <v>13</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>1</v>
+        <v>59</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>60</v>
@@ -1311,10 +1251,10 @@
         <v>15</v>
       </c>
       <c r="B16" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C16" s="1" t="s">
         <v>62</v>
-      </c>
-      <c r="C16" s="1" t="s">
-        <v>63</v>
       </c>
     </row>
     <row r="17" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -1322,7 +1262,7 @@
         <v>16</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>1</v>
+        <v>63</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>64</v>
@@ -1344,10 +1284,10 @@
         <v>18</v>
       </c>
       <c r="B19" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C19" s="1" t="s">
         <v>66</v>
-      </c>
-      <c r="C19" s="1" t="s">
-        <v>67</v>
       </c>
     </row>
     <row r="20" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -1355,7 +1295,7 @@
         <v>19</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>1</v>
+        <v>67</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>68</v>
@@ -1370,6 +1310,17 @@
       </c>
       <c r="C21" s="1" t="s">
         <v>69</v>
+      </c>
+    </row>
+    <row r="22" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A22" s="1">
+        <v>21</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>70</v>
       </c>
     </row>
   </sheetData>
@@ -1380,7 +1331,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E9"/>
+  <dimension ref="A1:E4"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
@@ -1395,7 +1346,7 @@
         <v>24</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C1" s="4" t="s">
         <v>26</v>
@@ -1412,7 +1363,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>44</v>
@@ -1429,10 +1380,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>45</v>
+        <v>74</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>35</v>
@@ -1446,100 +1397,15 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>47</v>
+        <v>74</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="5" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" s="1">
-        <v>4</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="E5" s="5" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="6" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" s="1">
-        <v>5</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="E6" s="5" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="7" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A7" s="1">
-        <v>6</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="E7" s="5" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="8" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A8" s="1">
-        <v>7</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="E8" s="5" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="9" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A9" s="1">
-        <v>8</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="E9" s="5" t="s">
         <v>32</v>
       </c>
     </row>
@@ -1551,7 +1417,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F27"/>
+  <dimension ref="A1:F28"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
@@ -1567,10 +1433,10 @@
         <v>24</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="D1" s="4" t="s">
         <v>26</v>
@@ -1587,16 +1453,16 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="F2" s="5" t="s">
         <v>32</v>
@@ -1633,7 +1499,7 @@
         <v>1</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="E4" s="1" t="s">
         <v>37</v>
@@ -1647,16 +1513,16 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="F5" s="5" t="s">
         <v>32</v>
@@ -1667,16 +1533,16 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="F6" s="5" t="s">
         <v>32</v>
@@ -1693,7 +1559,7 @@
         <v>1</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="E7" s="1" t="s">
         <v>40</v>
@@ -1710,7 +1576,7 @@
         <v>1</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="D8" s="1" t="s">
         <v>44</v>
@@ -1730,7 +1596,7 @@
         <v>1</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="D9" s="1" t="s">
         <v>45</v>
@@ -1750,13 +1616,13 @@
         <v>1</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>96</v>
+        <v>22</v>
       </c>
       <c r="F10" s="5" t="s">
         <v>32</v>
@@ -1770,13 +1636,13 @@
         <v>1</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>97</v>
+        <v>71</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>48</v>
+        <v>93</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>96</v>
+        <v>22</v>
       </c>
       <c r="F11" s="5" t="s">
         <v>32</v>
@@ -1790,13 +1656,13 @@
         <v>1</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>98</v>
+        <v>71</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>49</v>
+        <v>93</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>96</v>
+        <v>22</v>
       </c>
       <c r="F12" s="5" t="s">
         <v>32</v>
@@ -1810,13 +1676,13 @@
         <v>1</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>99</v>
+        <v>71</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>51</v>
+        <v>93</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>96</v>
+        <v>22</v>
       </c>
       <c r="F13" s="5" t="s">
         <v>32</v>
@@ -1830,13 +1696,13 @@
         <v>1</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>100</v>
+        <v>71</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>52</v>
+        <v>93</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>96</v>
+        <v>22</v>
       </c>
       <c r="F14" s="5" t="s">
         <v>32</v>
@@ -1850,13 +1716,13 @@
         <v>1</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>101</v>
+        <v>71</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>53</v>
+        <v>93</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>96</v>
+        <v>22</v>
       </c>
       <c r="F15" s="5" t="s">
         <v>32</v>
@@ -1870,13 +1736,13 @@
         <v>1</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>102</v>
+        <v>71</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>55</v>
+        <v>93</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>96</v>
+        <v>22</v>
       </c>
       <c r="F16" s="5" t="s">
         <v>32</v>
@@ -1890,13 +1756,13 @@
         <v>1</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>103</v>
+        <v>71</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>56</v>
+        <v>93</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>96</v>
+        <v>22</v>
       </c>
       <c r="F17" s="5" t="s">
         <v>32</v>
@@ -1910,13 +1776,13 @@
         <v>1</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>104</v>
+        <v>71</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>57</v>
+        <v>93</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>96</v>
+        <v>22</v>
       </c>
       <c r="F18" s="5" t="s">
         <v>32</v>
@@ -1930,13 +1796,13 @@
         <v>1</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>105</v>
+        <v>71</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>59</v>
+        <v>93</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>96</v>
+        <v>22</v>
       </c>
       <c r="F19" s="5" t="s">
         <v>32</v>
@@ -1950,13 +1816,13 @@
         <v>1</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>106</v>
+        <v>71</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>60</v>
+        <v>93</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>96</v>
+        <v>22</v>
       </c>
       <c r="F20" s="5" t="s">
         <v>32</v>
@@ -1970,13 +1836,13 @@
         <v>1</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>107</v>
+        <v>71</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>61</v>
+        <v>93</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>96</v>
+        <v>22</v>
       </c>
       <c r="F21" s="5" t="s">
         <v>32</v>
@@ -1990,13 +1856,13 @@
         <v>1</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>108</v>
+        <v>71</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>63</v>
+        <v>93</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>96</v>
+        <v>22</v>
       </c>
       <c r="F22" s="5" t="s">
         <v>32</v>
@@ -2010,13 +1876,13 @@
         <v>1</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>109</v>
+        <v>71</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>64</v>
+        <v>93</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>96</v>
+        <v>22</v>
       </c>
       <c r="F23" s="5" t="s">
         <v>32</v>
@@ -2030,13 +1896,13 @@
         <v>1</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>110</v>
+        <v>71</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>65</v>
+        <v>93</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>96</v>
+        <v>22</v>
       </c>
       <c r="F24" s="5" t="s">
         <v>32</v>
@@ -2050,13 +1916,13 @@
         <v>1</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>111</v>
+        <v>71</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>67</v>
+        <v>93</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>96</v>
+        <v>22</v>
       </c>
       <c r="F25" s="5" t="s">
         <v>32</v>
@@ -2070,13 +1936,13 @@
         <v>1</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>112</v>
+        <v>71</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>68</v>
+        <v>93</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>96</v>
+        <v>22</v>
       </c>
       <c r="F26" s="5" t="s">
         <v>32</v>
@@ -2090,15 +1956,35 @@
         <v>1</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>113</v>
+        <v>71</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>69</v>
+        <v>93</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>96</v>
+        <v>22</v>
       </c>
       <c r="F27" s="5" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="28" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A28" s="1">
+        <v>27</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="D28" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="E28" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="F28" s="5" t="s">
         <v>32</v>
       </c>
     </row>
@@ -2127,16 +2013,16 @@
         <v>1</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>114</v>
+        <v>94</v>
       </c>
       <c r="C1" s="2"/>
       <c r="D1" s="2"/>
       <c r="E1" s="2"/>
       <c r="F1" s="2" t="s">
-        <v>115</v>
+        <v>95</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>116</v>
+        <v>96</v>
       </c>
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
@@ -2144,45 +2030,45 @@
     </row>
     <row r="2" ht="25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
-        <v>117</v>
+        <v>97</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>118</v>
+        <v>98</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>119</v>
+        <v>99</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>121</v>
+        <v>101</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>122</v>
+        <v>102</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>123</v>
+        <v>103</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>118</v>
+        <v>98</v>
       </c>
       <c r="I2" s="4" t="s">
-        <v>119</v>
+        <v>99</v>
       </c>
       <c r="J2" s="4" t="s">
-        <v>120</v>
+        <v>100</v>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>124</v>
+        <v>104</v>
       </c>
       <c r="B3" s="1">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C3" s="1">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D3" s="1">
         <v>0</v>
@@ -2191,19 +2077,19 @@
         <v>0</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>125</v>
+        <v>105</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>126</v>
+        <v>106</v>
       </c>
       <c r="H3" s="1">
         <v>0</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>127</v>
+        <v>107</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>127</v>
+        <v>107</v>
       </c>
     </row>
   </sheetData>

--- a/Exam/gymtrackerpro/lib/repository/__tests__/bbt/user-repository/updateMember-bbt-form.xlsx
+++ b/Exam/gymtrackerpro/lib/repository/__tests__/bbt/user-repository/updateMember-bbt-form.xlsx
@@ -17,9 +17,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="280" uniqueCount="108">
-  <si>
-    <t>Statement: UserRepository.updateMember(memberId, data) – atomically updates Member and User.</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="335" uniqueCount="132">
+  <si>
+    <t>Statement: UserRepository.updateMember(id, data) – Updates a member and their user record. Returns the updated MemberWithUser on success. Throws NotFoundError if the member does not exist. Throws ConflictError if the new email is already taken by another user. Throws TransactionError if the database write fails.</t>
   </si>
   <si>
     <t/>
@@ -31,13 +31,13 @@
     <t>Data</t>
   </si>
   <si>
-    <t>Input: memberId: string, data: UpdateMemberInput</t>
+    <t>Input: id: string, data: UpdateMemberInput { fullName?, email?, phone?, dateOfBirth?, password?, membershipStart? }</t>
   </si>
   <si>
     <t>precondition</t>
   </si>
   <si>
-    <t>Database is accessible</t>
+    <t>Database is accessible. A member with the given ID may or may not exist. Any new email may or may not already be registered to another user.</t>
   </si>
   <si>
     <t>Results</t>
@@ -49,7 +49,7 @@
     <t>postcondition</t>
   </si>
   <si>
-    <t>Updates records or throws error.</t>
+    <t>On success: MemberWithUser returned with updated fields (result.user.fullName, result.id). On failure: NotFoundError, ConflictError, or TransactionError thrown.</t>
   </si>
   <si>
     <t>Number EC</t>
@@ -67,28 +67,37 @@
     <t>Member existence</t>
   </si>
   <si>
-    <t>Found</t>
-  </si>
-  <si>
-    <t>Not found (NotFoundError)</t>
-  </si>
-  <si>
-    <t>Email conflict</t>
-  </si>
-  <si>
-    <t>New email unique or same</t>
-  </si>
-  <si>
-    <t>New email taken (ConflictError)</t>
+    <t>Existing ID + valid data → MemberWithUser returned with result.user.fullName: "Updated Name"</t>
+  </si>
+  <si>
+    <t>Non-existent ID → NotFoundError</t>
+  </si>
+  <si>
+    <t>Email uniqueness</t>
+  </si>
+  <si>
+    <t>New email not taken → MemberWithUser returned</t>
+  </si>
+  <si>
+    <t>New email taken by another user → ConflictError</t>
+  </si>
+  <si>
+    <t>Email identity</t>
+  </si>
+  <si>
+    <t>Same email as current user → MemberWithUser returned with result.id: MEMBER_ID</t>
+  </si>
+  <si>
+    <t>Password change</t>
+  </si>
+  <si>
+    <t>New password provided → MemberWithUser returned with result.id: MEMBER_ID</t>
   </si>
   <si>
     <t>Database write</t>
   </si>
   <si>
-    <t>Success</t>
-  </si>
-  <si>
-    <t>Failure (TransactionError)</t>
+    <t>Write fails → TransactionError</t>
   </si>
   <si>
     <t>No TC</t>
@@ -106,13 +115,13 @@
     <t>Actual Result</t>
   </si>
   <si>
-    <t>EC-1, EC-3, EC-5</t>
-  </si>
-  <si>
-    <t>Existing member, valid data</t>
-  </si>
-  <si>
-    <t>Returns updated MemberWithUser</t>
+    <t>EC-1</t>
+  </si>
+  <si>
+    <t>id: MEMBER_ID, data: { fullName: "Updated Name" }</t>
+  </si>
+  <si>
+    <t>MemberWithUser returned with result.user.fullName: "Updated Name"</t>
   </si>
   <si>
     <t>Passed</t>
@@ -121,25 +130,43 @@
     <t>EC-2</t>
   </si>
   <si>
-    <t>Non-existent memberId</t>
-  </si>
-  <si>
-    <t>Throws NotFoundError</t>
+    <t>id: NONEXISTENT_ID, data: { fullName: "New Name" }</t>
+  </si>
+  <si>
+    <t>throws NotFoundError</t>
   </si>
   <si>
     <t>EC-4</t>
   </si>
   <si>
-    <t>Throws ConflictError</t>
+    <t>id: MEMBER_ID, data: { email: "taken@example.com" }</t>
+  </si>
+  <si>
+    <t>throws ConflictError</t>
+  </si>
+  <si>
+    <t>EC-5</t>
+  </si>
+  <si>
+    <t>id: MEMBER_ID, data: { email: MOCK_USER.email }</t>
+  </si>
+  <si>
+    <t>MemberWithUser returned with result.id: MEMBER_ID</t>
   </si>
   <si>
     <t>EC-6</t>
   </si>
   <si>
-    <t>Database failure</t>
-  </si>
-  <si>
-    <t>Throws TransactionError</t>
+    <t>id: MEMBER_ID, data: { password: "NewPass1!" }</t>
+  </si>
+  <si>
+    <t>EC-7</t>
+  </si>
+  <si>
+    <t>id: MEMBER_ID, data: { fullName: "New Name" }, DB fails</t>
+  </si>
+  <si>
+    <t>throws TransactionError</t>
   </si>
   <si>
     <t>Number BVA</t>
@@ -148,106 +175,175 @@
     <t>BVA Test Case</t>
   </si>
   <si>
-    <t>ID length</t>
-  </si>
-  <si>
-    <t>memberId = ""</t>
-  </si>
-  <si>
-    <t>memberId = "a" (inex)</t>
-  </si>
-  <si>
-    <t>memberId = "a" (exist)</t>
-  </si>
-  <si>
-    <t>Email field</t>
-  </si>
-  <si>
-    <t>email = undefined</t>
-  </si>
-  <si>
-    <t>email = ""</t>
-  </si>
-  <si>
-    <t>email = "a"</t>
-  </si>
-  <si>
-    <t>FullName field</t>
-  </si>
-  <si>
-    <t>fullName = undefined</t>
-  </si>
-  <si>
-    <t>fullName = ""</t>
-  </si>
-  <si>
-    <t>fullName = "A"</t>
-  </si>
-  <si>
-    <t>Phone field</t>
-  </si>
-  <si>
-    <t>phone = undefined</t>
-  </si>
-  <si>
-    <t>phone = ""</t>
-  </si>
-  <si>
-    <t>phone = "a"</t>
-  </si>
-  <si>
-    <t>DOB field</t>
-  </si>
-  <si>
-    <t>dateOfBirth = undefined</t>
-  </si>
-  <si>
-    <t>dateOfBirth = ""</t>
-  </si>
-  <si>
-    <t>dateOfBirth = "a"</t>
-  </si>
-  <si>
-    <t>Password field</t>
-  </si>
-  <si>
-    <t>password = undefined</t>
-  </si>
-  <si>
-    <t>password = ""</t>
-  </si>
-  <si>
-    <t>password = "a"</t>
-  </si>
-  <si>
-    <t>Membership field</t>
-  </si>
-  <si>
-    <t>membershipStart = undefined</t>
-  </si>
-  <si>
-    <t>membershipStart = ""</t>
-  </si>
-  <si>
-    <t>membershipStart = "a"</t>
+    <t>Member ID length</t>
+  </si>
+  <si>
+    <t>0 chars (empty, not found), 1 char (not found), 1 char (found)</t>
+  </si>
+  <si>
+    <t>email field</t>
+  </si>
+  <si>
+    <t>email: undefined, email: "" (empty), email: "a" (one char)</t>
+  </si>
+  <si>
+    <t>fullName field</t>
+  </si>
+  <si>
+    <t>fullName: undefined, fullName: "" (empty), fullName: "A" (one char)</t>
+  </si>
+  <si>
+    <t>phone field</t>
+  </si>
+  <si>
+    <t>phone: undefined, phone: "" (empty), phone: "a" (one char)</t>
+  </si>
+  <si>
+    <t>dateOfBirth field</t>
+  </si>
+  <si>
+    <t>dateOfBirth: undefined, dateOfBirth: "" (empty), dateOfBirth: "a" (one char)</t>
+  </si>
+  <si>
+    <t>password field</t>
+  </si>
+  <si>
+    <t>password: undefined, password: "" (empty), password: "a" (one char)</t>
+  </si>
+  <si>
+    <t>membershipStart field</t>
+  </si>
+  <si>
+    <t>membershipStart: undefined, membershipStart: "" (empty), membershipStart: "a" (one char)</t>
   </si>
   <si>
     <t>BVA</t>
   </si>
   <si>
-    <t>BVA-1 EmptyID</t>
-  </si>
-  <si>
-    <t>BVA-2 InexCharID</t>
-  </si>
-  <si>
-    <t>memberId = "a"</t>
-  </si>
-  <si>
-    <t>BVA-3 ExistCharID</t>
-  </si>
-  <si>
-    <t>Updates successfully</t>
+    <t>BVA-1 (n=0)</t>
+  </si>
+  <si>
+    <t>id: "", data: { fullName: "New Name" }</t>
+  </si>
+  <si>
+    <t>BVA-1 (n=1)</t>
+  </si>
+  <si>
+    <t>id: "a" (no match), data: { fullName: "New Name" }</t>
+  </si>
+  <si>
+    <t>id: "a" (found), data: { fullName: "New Name" }</t>
+  </si>
+  <si>
+    <t>MemberWithUser returned with result.id: "a"</t>
+  </si>
+  <si>
+    <t>BVA-2 (undef)</t>
+  </si>
+  <si>
+    <t>id: MEMBER_ID, data: { email: undefined }</t>
+  </si>
+  <si>
+    <t>BVA-2 (n=0)</t>
+  </si>
+  <si>
+    <t>id: MEMBER_ID, data: { email: "" }</t>
+  </si>
+  <si>
+    <t>BVA-2 (n=1)</t>
+  </si>
+  <si>
+    <t>id: MEMBER_ID, data: { email: "a" }</t>
+  </si>
+  <si>
+    <t>BVA-3 (undef)</t>
+  </si>
+  <si>
+    <t>id: MEMBER_ID, data: { fullName: undefined }</t>
+  </si>
+  <si>
+    <t>BVA-3 (n=0)</t>
+  </si>
+  <si>
+    <t>id: MEMBER_ID, data: { fullName: "" }</t>
+  </si>
+  <si>
+    <t>BVA-3 (n=1)</t>
+  </si>
+  <si>
+    <t>id: MEMBER_ID, data: { fullName: "A" }</t>
+  </si>
+  <si>
+    <t>BVA-4 (undef)</t>
+  </si>
+  <si>
+    <t>id: MEMBER_ID, data: { phone: undefined }</t>
+  </si>
+  <si>
+    <t>BVA-4 (n=0)</t>
+  </si>
+  <si>
+    <t>id: MEMBER_ID, data: { phone: "" }</t>
+  </si>
+  <si>
+    <t>BVA-4 (n=1)</t>
+  </si>
+  <si>
+    <t>id: MEMBER_ID, data: { phone: "a" }</t>
+  </si>
+  <si>
+    <t>BVA-5 (undef)</t>
+  </si>
+  <si>
+    <t>id: MEMBER_ID, data: { dateOfBirth: undefined }</t>
+  </si>
+  <si>
+    <t>BVA-5 (n=0)</t>
+  </si>
+  <si>
+    <t>id: MEMBER_ID, data: { dateOfBirth: "" }</t>
+  </si>
+  <si>
+    <t>BVA-5 (n=1)</t>
+  </si>
+  <si>
+    <t>id: MEMBER_ID, data: { dateOfBirth: "a" }</t>
+  </si>
+  <si>
+    <t>BVA-6 (undef)</t>
+  </si>
+  <si>
+    <t>id: MEMBER_ID, data: { password: undefined }</t>
+  </si>
+  <si>
+    <t>BVA-6 (n=0)</t>
+  </si>
+  <si>
+    <t>id: MEMBER_ID, data: { password: "" }</t>
+  </si>
+  <si>
+    <t>BVA-6 (n=1)</t>
+  </si>
+  <si>
+    <t>id: MEMBER_ID, data: { password: "a" }</t>
+  </si>
+  <si>
+    <t>BVA-7 (undef)</t>
+  </si>
+  <si>
+    <t>id: MEMBER_ID, data: { membershipStart: undefined }</t>
+  </si>
+  <si>
+    <t>BVA-7 (n=0)</t>
+  </si>
+  <si>
+    <t>id: MEMBER_ID, data: { membershipStart: "" }</t>
+  </si>
+  <si>
+    <t>BVA-7 (n=1)</t>
+  </si>
+  <si>
+    <t>id: MEMBER_ID, data: { membershipStart: "a" }</t>
   </si>
   <si>
     <t>TC from EC</t>
@@ -256,39 +352,6 @@
     <t>TC from BVA</t>
   </si>
   <si>
-    <t>EC-1</t>
-  </si>
-  <si>
-    <t>Existing member, update fullName</t>
-  </si>
-  <si>
-    <t>Member record updated</t>
-  </si>
-  <si>
-    <t>Email taken by other user</t>
-  </si>
-  <si>
-    <t>EC-3</t>
-  </si>
-  <si>
-    <t>Update to current email</t>
-  </si>
-  <si>
-    <t>Skips conflict check</t>
-  </si>
-  <si>
-    <t>EC-5</t>
-  </si>
-  <si>
-    <t>Update with new password</t>
-  </si>
-  <si>
-    <t>Password is hashed</t>
-  </si>
-  <si>
-    <t>Database write error</t>
-  </si>
-  <si>
     <t>BVA-1</t>
   </si>
   <si>
@@ -298,7 +361,16 @@
     <t>BVA-3</t>
   </si>
   <si>
-    <t>Various field updates</t>
+    <t>BVA-4</t>
+  </si>
+  <si>
+    <t>BVA-5</t>
+  </si>
+  <si>
+    <t>BVA-6</t>
+  </si>
+  <si>
+    <t>BVA-7</t>
   </si>
   <si>
     <t>Testing</t>
@@ -331,7 +403,7 @@
     <t>Re-tested</t>
   </si>
   <si>
-    <t>MEM-05</t>
+    <t>REPO-09</t>
   </si>
   <si>
     <t>n/a</t>
@@ -856,7 +928,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D7"/>
+  <dimension ref="A1:D8"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -897,7 +969,7 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>1</v>
@@ -925,7 +997,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>1</v>
@@ -953,13 +1025,27 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>1</v>
+        <v>23</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>23</v>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A8" s="1">
+        <v>7</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>26</v>
       </c>
     </row>
   </sheetData>
@@ -970,7 +1056,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E5"/>
+  <dimension ref="A1:E7"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
@@ -982,19 +1068,19 @@
   <sheetData>
     <row r="1" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
     </row>
     <row r="2" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -1002,16 +1088,16 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
     </row>
     <row r="3" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -1019,16 +1105,16 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
     </row>
     <row r="4" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -1036,16 +1122,16 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>18</v>
+        <v>40</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
     </row>
     <row r="5" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -1053,16 +1139,50 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>32</v>
+        <v>35</v>
+      </c>
+    </row>
+    <row r="6" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" s="1">
+        <v>5</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="7" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" s="1">
+        <v>6</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>35</v>
       </c>
     </row>
   </sheetData>
@@ -1073,7 +1193,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C22"/>
+  <dimension ref="A1:C8"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -1083,13 +1203,13 @@
   <sheetData>
     <row r="1" ht="20" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="B1" s="4" t="s">
         <v>12</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>42</v>
+        <v>51</v>
       </c>
     </row>
     <row r="2" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -1097,10 +1217,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>44</v>
+        <v>53</v>
       </c>
     </row>
     <row r="3" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -1108,10 +1228,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>1</v>
+        <v>54</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>45</v>
+        <v>55</v>
       </c>
     </row>
     <row r="4" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -1119,10 +1239,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>1</v>
+        <v>56</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>46</v>
+        <v>57</v>
       </c>
     </row>
     <row r="5" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -1130,10 +1250,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>47</v>
+        <v>58</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>48</v>
+        <v>59</v>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -1141,10 +1261,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>1</v>
+        <v>60</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>49</v>
+        <v>61</v>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -1152,10 +1272,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>1</v>
+        <v>62</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>50</v>
+        <v>63</v>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -1163,164 +1283,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>51</v>
+        <v>64</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="9" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A9" s="1">
-        <v>8</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="10" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A10" s="1">
-        <v>9</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="11" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A11" s="1">
-        <v>10</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="12" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A12" s="1">
-        <v>11</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="13" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A13" s="1">
-        <v>12</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C13" s="1" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="14" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A14" s="1">
-        <v>13</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="C14" s="1" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="15" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A15" s="1">
-        <v>14</v>
-      </c>
-      <c r="B15" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C15" s="1" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="16" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A16" s="1">
-        <v>15</v>
-      </c>
-      <c r="B16" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C16" s="1" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="17" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A17" s="1">
-        <v>16</v>
-      </c>
-      <c r="B17" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="C17" s="1" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="18" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A18" s="1">
-        <v>17</v>
-      </c>
-      <c r="B18" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C18" s="1" t="s">
         <v>65</v>
-      </c>
-    </row>
-    <row r="19" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A19" s="1">
-        <v>18</v>
-      </c>
-      <c r="B19" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C19" s="1" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="20" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A20" s="1">
-        <v>19</v>
-      </c>
-      <c r="B20" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="C20" s="1" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="21" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A21" s="1">
-        <v>20</v>
-      </c>
-      <c r="B21" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C21" s="1" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="22" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A22" s="1">
-        <v>21</v>
-      </c>
-      <c r="B22" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C22" s="1" t="s">
-        <v>70</v>
       </c>
     </row>
   </sheetData>
@@ -1331,7 +1297,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E4"/>
+  <dimension ref="A1:E22"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
@@ -1343,19 +1309,19 @@
   <sheetData>
     <row r="1" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
     </row>
     <row r="2" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -1363,16 +1329,16 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>44</v>
+        <v>68</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
     </row>
     <row r="3" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -1380,16 +1346,16 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
     </row>
     <row r="4" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -1397,16 +1363,322 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="5" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" s="1">
+        <v>4</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="6" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" s="1">
+        <v>5</v>
+      </c>
+      <c r="B6" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="C4" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="D4" s="1" t="s">
+      <c r="C6" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="E4" s="5" t="s">
-        <v>32</v>
+      <c r="D6" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="7" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" s="1">
+        <v>6</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="8" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8" s="1">
+        <v>7</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="E8" s="5" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="9" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A9" s="1">
+        <v>8</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="E9" s="5" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="10" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A10" s="1">
+        <v>9</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="E10" s="5" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="11" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A11" s="1">
+        <v>10</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="E11" s="5" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="12" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A12" s="1">
+        <v>11</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="E12" s="5" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="13" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A13" s="1">
+        <v>12</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="E13" s="5" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="14" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A14" s="1">
+        <v>13</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="E14" s="5" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="15" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A15" s="1">
+        <v>14</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="E15" s="5" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="16" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A16" s="1">
+        <v>15</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="E16" s="5" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="17" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A17" s="1">
+        <v>16</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="E17" s="5" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="18" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A18" s="1">
+        <v>17</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="E18" s="5" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="19" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A19" s="1">
+        <v>18</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="E19" s="5" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="20" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A20" s="1">
+        <v>19</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="E20" s="5" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="21" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A21" s="1">
+        <v>20</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="E21" s="5" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="22" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A22" s="1">
+        <v>21</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="E22" s="5" t="s">
+        <v>35</v>
       </c>
     </row>
   </sheetData>
@@ -1430,22 +1702,22 @@
   <sheetData>
     <row r="1" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>77</v>
+        <v>109</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>78</v>
+        <v>110</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
     </row>
     <row r="2" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1453,19 +1725,19 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>79</v>
+        <v>32</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>80</v>
+        <v>33</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>81</v>
+        <v>34</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
     </row>
     <row r="3" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1473,19 +1745,19 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
     </row>
     <row r="4" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1493,19 +1765,19 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>82</v>
+        <v>40</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
     </row>
     <row r="5" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1513,19 +1785,19 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>83</v>
+        <v>42</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>84</v>
+        <v>43</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>85</v>
+        <v>44</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
     </row>
     <row r="6" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1533,19 +1805,19 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>86</v>
+        <v>45</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>87</v>
+        <v>46</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
     </row>
     <row r="7" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1553,19 +1825,19 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>89</v>
+        <v>48</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
     </row>
     <row r="8" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1576,16 +1848,16 @@
         <v>1</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>90</v>
+        <v>111</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>44</v>
+        <v>68</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="F8" s="5" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
     </row>
     <row r="9" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1596,16 +1868,16 @@
         <v>1</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>91</v>
+        <v>111</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>45</v>
+        <v>70</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
     </row>
     <row r="10" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1616,16 +1888,16 @@
         <v>1</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>92</v>
+        <v>111</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>46</v>
+        <v>71</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>22</v>
+        <v>72</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
     </row>
     <row r="11" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1636,16 +1908,16 @@
         <v>1</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>71</v>
+        <v>112</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>93</v>
+        <v>74</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>22</v>
+        <v>44</v>
       </c>
       <c r="F11" s="5" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
     </row>
     <row r="12" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1656,16 +1928,16 @@
         <v>1</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>71</v>
+        <v>112</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>93</v>
+        <v>76</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>22</v>
+        <v>44</v>
       </c>
       <c r="F12" s="5" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
     </row>
     <row r="13" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1676,16 +1948,16 @@
         <v>1</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>71</v>
+        <v>112</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>93</v>
+        <v>78</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>22</v>
+        <v>44</v>
       </c>
       <c r="F13" s="5" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
     </row>
     <row r="14" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1696,16 +1968,16 @@
         <v>1</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>71</v>
+        <v>113</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>22</v>
+        <v>44</v>
       </c>
       <c r="F14" s="5" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
     </row>
     <row r="15" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1716,16 +1988,16 @@
         <v>1</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>71</v>
+        <v>113</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>22</v>
+        <v>44</v>
       </c>
       <c r="F15" s="5" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
     </row>
     <row r="16" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1736,16 +2008,16 @@
         <v>1</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>71</v>
+        <v>113</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>93</v>
+        <v>84</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>22</v>
+        <v>44</v>
       </c>
       <c r="F16" s="5" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
     </row>
     <row r="17" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1756,16 +2028,16 @@
         <v>1</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>71</v>
+        <v>114</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>93</v>
+        <v>86</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>22</v>
+        <v>44</v>
       </c>
       <c r="F17" s="5" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
     </row>
     <row r="18" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1776,16 +2048,16 @@
         <v>1</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>71</v>
+        <v>114</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>22</v>
+        <v>44</v>
       </c>
       <c r="F18" s="5" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
     </row>
     <row r="19" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1796,16 +2068,16 @@
         <v>1</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>71</v>
+        <v>114</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>22</v>
+        <v>44</v>
       </c>
       <c r="F19" s="5" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
     </row>
     <row r="20" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1816,16 +2088,16 @@
         <v>1</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>71</v>
+        <v>115</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>22</v>
+        <v>44</v>
       </c>
       <c r="F20" s="5" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
     </row>
     <row r="21" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1836,16 +2108,16 @@
         <v>1</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>71</v>
+        <v>115</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>22</v>
+        <v>44</v>
       </c>
       <c r="F21" s="5" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
     </row>
     <row r="22" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1856,16 +2128,16 @@
         <v>1</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>71</v>
+        <v>115</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>22</v>
+        <v>44</v>
       </c>
       <c r="F22" s="5" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
     </row>
     <row r="23" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1876,16 +2148,16 @@
         <v>1</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>71</v>
+        <v>116</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>22</v>
+        <v>44</v>
       </c>
       <c r="F23" s="5" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
     </row>
     <row r="24" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1896,16 +2168,16 @@
         <v>1</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>71</v>
+        <v>116</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>93</v>
+        <v>100</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>22</v>
+        <v>44</v>
       </c>
       <c r="F24" s="5" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
     </row>
     <row r="25" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1916,16 +2188,16 @@
         <v>1</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>71</v>
+        <v>116</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>93</v>
+        <v>102</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>22</v>
+        <v>44</v>
       </c>
       <c r="F25" s="5" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
     </row>
     <row r="26" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1936,16 +2208,16 @@
         <v>1</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>71</v>
+        <v>117</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>93</v>
+        <v>104</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>22</v>
+        <v>44</v>
       </c>
       <c r="F26" s="5" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
     </row>
     <row r="27" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1956,16 +2228,16 @@
         <v>1</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>71</v>
+        <v>117</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>93</v>
+        <v>106</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>22</v>
+        <v>44</v>
       </c>
       <c r="F27" s="5" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
     </row>
     <row r="28" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1976,16 +2248,16 @@
         <v>1</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>71</v>
+        <v>117</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>93</v>
+        <v>108</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>22</v>
+        <v>44</v>
       </c>
       <c r="F28" s="5" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
     </row>
   </sheetData>
@@ -2013,16 +2285,16 @@
         <v>1</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>94</v>
+        <v>118</v>
       </c>
       <c r="C1" s="2"/>
       <c r="D1" s="2"/>
       <c r="E1" s="2"/>
       <c r="F1" s="2" t="s">
-        <v>95</v>
+        <v>119</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>96</v>
+        <v>120</v>
       </c>
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
@@ -2030,39 +2302,39 @@
     </row>
     <row r="2" ht="25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
-        <v>97</v>
+        <v>121</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>98</v>
+        <v>122</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>99</v>
+        <v>123</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>100</v>
+        <v>124</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>101</v>
+        <v>125</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>102</v>
+        <v>126</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>103</v>
+        <v>127</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>98</v>
+        <v>122</v>
       </c>
       <c r="I2" s="4" t="s">
-        <v>99</v>
+        <v>123</v>
       </c>
       <c r="J2" s="4" t="s">
-        <v>100</v>
+        <v>124</v>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>104</v>
+        <v>128</v>
       </c>
       <c r="B3" s="1">
         <v>27</v>
@@ -2077,19 +2349,19 @@
         <v>0</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>105</v>
+        <v>129</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>106</v>
+        <v>130</v>
       </c>
       <c r="H3" s="1">
         <v>0</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>107</v>
+        <v>131</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>107</v>
+        <v>131</v>
       </c>
     </row>
   </sheetData>
